--- a/DFW_Rolodex.xlsx
+++ b/DFW_Rolodex.xlsx
@@ -14131,7 +14131,7 @@
       </c>
       <c r="S112" s="15" t="inlineStr">
         <is>
-          <t>Pours tilt-wall, schools and paving from Euless and Arlington. Invests in LiDAR, robotics and new equipment.</t>
+          <t>Pours tilt-wall, schools and paving from Euless and Arlington.</t>
         </is>
       </c>
       <c r="T112" s="12" t="inlineStr">
@@ -14260,7 +14260,7 @@
       </c>
       <c r="S113" s="9" t="inlineStr">
         <is>
-          <t>Pours tilt-wall, schools and paving from Euless and Arlington. Invests in LiDAR, robotics and new equipment.</t>
+          <t>Pours tilt-wall, schools and paving from Euless and Arlington.</t>
         </is>
       </c>
       <c r="T113" s="6" t="inlineStr">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="S143" s="9" t="inlineStr">
         <is>
-          <t>Pours tilt panels and structural concrete nationally, with its Texas jobs mostly in Houston. Machine purchases run through a national desk.</t>
+          <t>Pours tilt panels and structural concrete nationally, with its Texas jobs mostly in Houston.</t>
         </is>
       </c>
       <c r="T143" s="6" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="S144" s="15" t="inlineStr">
         <is>
-          <t>Pours tilt panels and structural concrete nationally, with its Texas jobs mostly in Houston. Machine purchases run through a national desk.</t>
+          <t>Pours tilt panels and structural concrete nationally, with its Texas jobs mostly in Houston.</t>
         </is>
       </c>
       <c r="T144" s="12" t="inlineStr">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="S145" s="9" t="inlineStr">
         <is>
-          <t>Pours tilt panels and structural concrete nationally, with its Texas jobs mostly in Houston. Machine purchases run through a national desk.</t>
+          <t>Pours tilt panels and structural concrete nationally, with its Texas jobs mostly in Houston.</t>
         </is>
       </c>
       <c r="T145" s="6" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="S146" s="15" t="inlineStr">
         <is>
-          <t>Pours tilt panels and structural concrete nationally, with its Texas jobs mostly in Houston. Machine purchases run through a national desk.</t>
+          <t>Pours tilt panels and structural concrete nationally, with its Texas jobs mostly in Houston.</t>
         </is>
       </c>
       <c r="T146" s="12" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="S167" s="9" t="inlineStr">
         <is>
-          <t>Owned a framing plant and piloted a robotic wall. Materials are negotiated nationally or regionally.</t>
+          <t>Materials are negotiated nationally or regionally.</t>
         </is>
       </c>
       <c r="T167" s="6" t="inlineStr">
@@ -28840,7 +28840,7 @@
       </c>
       <c r="S229" s="9" t="inlineStr">
         <is>
-          <t>Roster builders: American Legend, Coventry, Drees, Highland and Perry. Hillwood develops the lots.</t>
+          <t>Roster builders: American Legend, Coventry, Drees, Highland and Perry.</t>
         </is>
       </c>
       <c r="T229" s="6" t="inlineStr"/>
@@ -28965,7 +28965,7 @@
       </c>
       <c r="S230" s="15" t="inlineStr">
         <is>
-          <t>Roster builders: American Legend, Coventry, Drees, Highland and Perry. Hillwood develops the lots.</t>
+          <t>Roster builders: American Legend, Coventry, Drees, Highland and Perry.</t>
         </is>
       </c>
       <c r="T230" s="12" t="inlineStr">

--- a/DFW_Rolodex.xlsx
+++ b/DFW_Rolodex.xlsx
@@ -563,7 +563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Héctor Ibarzábal · 2026-09-28</t>
+          <t>Héctor Ibarzábal · 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -32887,7 +32887,7 @@
     <row r="284">
       <c r="A284" s="14" t="inlineStr">
         <is>
-          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Dallas-Fort Worth, 2026-09-28.</t>
+          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Dallas-Fort Worth, 2026-09-30.</t>
         </is>
       </c>
     </row>

--- a/DFW_Rolodex.xlsx
+++ b/DFW_Rolodex.xlsx
@@ -563,7 +563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Héctor Ibarzábal · 2026-09-30</t>
+          <t>Héctor Ibarzábal · 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -32887,7 +32887,7 @@
     <row r="284">
       <c r="A284" s="14" t="inlineStr">
         <is>
-          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Dallas-Fort Worth, 2026-09-30.</t>
+          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Dallas-Fort Worth, 2026-10-09.</t>
         </is>
       </c>
     </row>

--- a/DFW_Rolodex.xlsx
+++ b/DFW_Rolodex.xlsx
@@ -563,7 +563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Héctor Ibarzábal · 2026-10-09</t>
+          <t>Héctor Ibarzábal · 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -32887,7 +32887,7 @@
     <row r="284">
       <c r="A284" s="14" t="inlineStr">
         <is>
-          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Dallas-Fort Worth, 2026-10-09.</t>
+          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Dallas-Fort Worth, 2026-10-10.</t>
         </is>
       </c>
     </row>
